--- a/scripts/templates/cdisc_crf_specializations_latest_template.xlsx
+++ b/scripts/templates/cdisc_crf_specializations_latest_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\scripts\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC91822-2952-4AEF-9A8F-389971D5C4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC244ABD-C009-46F9-BDE6-828BF5D734B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="Domains" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CRF Specializations'!$A$1:$AJ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CRF Specializations'!$A$1:$AI$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
   <si>
     <t>package_date</t>
   </si>
@@ -1252,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
@@ -1287,10 +1287,9 @@
     <col min="33" max="33" width="23.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="24.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="28.7109375" style="3" customWidth="1"/>
-    <col min="36" max="36" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1396,12 +1395,9 @@
       <c r="AI1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AJ1" s="1" t="s">
-        <v>28</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AI1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/scripts/templates/cdisc_crf_specializations_latest_template.xlsx
+++ b/scripts/templates/cdisc_crf_specializations_latest_template.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\scripts\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC244ABD-C009-46F9-BDE6-828BF5D734B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3405959D-31C6-4B5A-90B3-A097E7B91AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="5" r:id="rId1"/>
     <sheet name="CRF Specializations" sheetId="2" r:id="rId2"/>
-    <sheet name="Domains" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CRF Specializations'!$A$1:$AI$1</definedName>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
   <si>
     <t>package_date</t>
   </si>
@@ -468,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -479,9 +478,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -763,20 +759,20 @@
   <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" style="18" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" style="18" customWidth="1"/>
-    <col min="3" max="3" width="61.42578125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="19" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="12"/>
+    <col min="1" max="1" width="16" style="17" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="61.42578125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="11.42578125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -788,449 +784,449 @@
       <c r="C2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="22" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="24"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="26"/>
+      <c r="D4" s="25"/>
     </row>
     <row r="5" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="23"/>
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="25"/>
     </row>
     <row r="6" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="26"/>
+      <c r="D6" s="25"/>
     </row>
     <row r="7" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="25"/>
     </row>
     <row r="9" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="25"/>
     </row>
     <row r="10" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="23"/>
+      <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="25"/>
     </row>
     <row r="11" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="25"/>
     </row>
     <row r="12" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="25"/>
     </row>
     <row r="13" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24"/>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="25"/>
     </row>
     <row r="14" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="26"/>
     </row>
     <row r="15" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="27" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="30"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="12"/>
+      <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="30"/>
+      <c r="D17" s="29"/>
     </row>
     <row r="18" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="30"/>
+      <c r="D18" s="29"/>
     </row>
     <row r="19" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="30"/>
+      <c r="D19" s="29"/>
     </row>
     <row r="20" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="12"/>
+      <c r="B20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="30"/>
+      <c r="D20" s="29"/>
     </row>
     <row r="21" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="30"/>
+      <c r="D21" s="29"/>
     </row>
     <row r="22" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="30"/>
+      <c r="D22" s="29"/>
     </row>
     <row r="23" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="12"/>
+      <c r="B23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="30"/>
+      <c r="D23" s="29"/>
     </row>
     <row r="24" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="12"/>
+      <c r="B24" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="29"/>
     </row>
     <row r="25" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="12"/>
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="29"/>
     </row>
     <row r="26" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="12"/>
+      <c r="B26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="30"/>
+      <c r="D26" s="29"/>
     </row>
     <row r="27" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="5" t="s">
+      <c r="A27" s="12"/>
+      <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="30"/>
+      <c r="D27" s="29"/>
     </row>
     <row r="28" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="5" t="s">
+      <c r="A28" s="12"/>
+      <c r="B28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="29"/>
+      <c r="D28" s="28"/>
     </row>
     <row r="29" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="5" t="s">
+      <c r="A29" s="12"/>
+      <c r="B29" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="12"/>
+      <c r="B30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="34"/>
+      <c r="D30" s="33"/>
     </row>
     <row r="31" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="5" t="s">
+      <c r="A32" s="12"/>
+      <c r="B32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="29"/>
+      <c r="D32" s="28"/>
     </row>
     <row r="33" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="12"/>
+      <c r="B33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="12"/>
+      <c r="B34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="30" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="5" t="s">
+      <c r="A35" s="12"/>
+      <c r="B35" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="32"/>
+      <c r="D35" s="31"/>
     </row>
     <row r="36" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="12"/>
+      <c r="B36" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="27" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="5" t="s">
+      <c r="A37" s="12"/>
+      <c r="B37" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="30"/>
+      <c r="D37" s="29"/>
     </row>
     <row r="38" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="5" t="s">
+      <c r="A38" s="12"/>
+      <c r="B38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="29"/>
+      <c r="D38" s="28"/>
     </row>
     <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
     </row>
     <row r="40" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13"/>
-      <c r="D41" s="5"/>
+      <c r="A41" s="12"/>
+      <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="13"/>
-      <c r="D42" s="5"/>
+      <c r="A42" s="12"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="D43" s="14"/>
+      <c r="A43" s="12"/>
+      <c r="D43" s="13"/>
     </row>
     <row r="44" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="D44" s="14"/>
+      <c r="A44" s="12"/>
+      <c r="D44" s="13"/>
     </row>
     <row r="45" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="13"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="14"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="13"/>
     </row>
     <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="13"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="14"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="13"/>
     </row>
     <row r="47" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="13"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="14"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="13"/>
     </row>
     <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="13"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="14"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="13"/>
     </row>
     <row r="49" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="13"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="14"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="13"/>
     </row>
     <row r="50" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="16"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="17"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="16"/>
     </row>
     <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -1401,22 +1397,4 @@
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D4D58F-1B91-4026-A7FA-AD7CF788CB4A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/scripts/templates/cdisc_crf_specializations_latest_template.xlsx
+++ b/scripts/templates/cdisc_crf_specializations_latest_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\scripts\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3405959D-31C6-4B5A-90B3-A097E7B91AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AAD38C-BED7-4391-B35F-9F8D0FF5112C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="85">
   <si>
     <t>package_date</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>sdtm_annotation</t>
-  </si>
-  <si>
-    <t>sdtm_mapping</t>
   </si>
   <si>
     <t>standard</t>
@@ -285,9 +282,6 @@
   </si>
   <si>
     <t>Annotation of the SDTM target on the CRF</t>
-  </si>
-  <si>
-    <t>Rule for mapping from CRF item to SDTM target variable</t>
   </si>
 </sst>
 </file>
@@ -467,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -523,6 +517,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -555,12 +552,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -767,174 +758,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21"/>
+      <c r="A1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
-        <v>61</v>
+      <c r="A3" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>62</v>
+        <v>40</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="25"/>
+        <v>39</v>
+      </c>
+      <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="23"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="25"/>
+        <v>50</v>
+      </c>
+      <c r="D5" s="26"/>
     </row>
     <row r="6" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="23"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="25"/>
+        <v>65</v>
+      </c>
+      <c r="D6" s="26"/>
     </row>
     <row r="7" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="25"/>
+        <v>66</v>
+      </c>
+      <c r="D7" s="26"/>
     </row>
     <row r="8" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="25"/>
+        <v>67</v>
+      </c>
+      <c r="D8" s="26"/>
     </row>
     <row r="9" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="25"/>
+        <v>68</v>
+      </c>
+      <c r="D9" s="26"/>
     </row>
     <row r="10" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="25"/>
+        <v>69</v>
+      </c>
+      <c r="D10" s="26"/>
     </row>
     <row r="11" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="26"/>
+    </row>
+    <row r="12" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="24"/>
+      <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="25"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="26"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="24"/>
+      <c r="B13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="25"/>
-    </row>
-    <row r="13" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="25"/>
+      <c r="D13" s="26"/>
     </row>
     <row r="14" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="26"/>
+        <v>74</v>
+      </c>
+      <c r="D14" s="27"/>
     </row>
     <row r="15" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>63</v>
+      <c r="D15" s="28" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="29"/>
+        <v>78</v>
+      </c>
+      <c r="D16" s="30"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
@@ -942,9 +933,9 @@
         <v>5</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="29"/>
+        <v>38</v>
+      </c>
+      <c r="D17" s="30"/>
     </row>
     <row r="18" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
@@ -952,9 +943,9 @@
         <v>18</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="29"/>
+        <v>51</v>
+      </c>
+      <c r="D18" s="30"/>
     </row>
     <row r="19" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
@@ -962,19 +953,19 @@
         <v>19</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="29"/>
+        <v>52</v>
+      </c>
+      <c r="D19" s="30"/>
     </row>
     <row r="20" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="29"/>
+        <v>63</v>
+      </c>
+      <c r="D20" s="30"/>
     </row>
     <row r="21" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
@@ -982,9 +973,9 @@
         <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="29"/>
+        <v>79</v>
+      </c>
+      <c r="D21" s="30"/>
     </row>
     <row r="22" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12"/>
@@ -992,9 +983,9 @@
         <v>12</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="29"/>
+        <v>80</v>
+      </c>
+      <c r="D22" s="30"/>
     </row>
     <row r="23" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
@@ -1002,9 +993,9 @@
         <v>9</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="29"/>
+        <v>34</v>
+      </c>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
@@ -1012,9 +1003,9 @@
         <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="29"/>
+        <v>33</v>
+      </c>
+      <c r="D24" s="30"/>
     </row>
     <row r="25" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
@@ -1022,9 +1013,9 @@
         <v>11</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="29"/>
+        <v>32</v>
+      </c>
+      <c r="D25" s="30"/>
     </row>
     <row r="26" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
@@ -1032,29 +1023,29 @@
         <v>21</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="29"/>
+        <v>53</v>
+      </c>
+      <c r="D26" s="30"/>
     </row>
     <row r="27" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="29"/>
+        <v>54</v>
+      </c>
+      <c r="D27" s="30"/>
     </row>
     <row r="28" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
       <c r="B28" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="28"/>
+        <v>55</v>
+      </c>
+      <c r="D28" s="29"/>
     </row>
     <row r="29" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12"/>
@@ -1062,10 +1053,10 @@
         <v>6</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="32" t="s">
         <v>37</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1074,9 +1065,9 @@
         <v>7</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="33"/>
+        <v>35</v>
+      </c>
+      <c r="D30" s="32"/>
     </row>
     <row r="31" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12"/>
@@ -1084,10 +1075,10 @@
         <v>8</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1096,9 +1087,9 @@
         <v>22</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="28"/>
+        <v>56</v>
+      </c>
+      <c r="D32" s="29"/>
     </row>
     <row r="33" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
@@ -1106,7 +1097,7 @@
         <v>23</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D33" s="4"/>
     </row>
@@ -1116,21 +1107,21 @@
         <v>24</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>50</v>
+        <v>82</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12"/>
       <c r="B35" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D35" s="31"/>
+        <v>58</v>
+      </c>
+      <c r="D35" s="29"/>
     </row>
     <row r="36" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12"/>
@@ -1138,10 +1129,10 @@
         <v>26</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>49</v>
+        <v>83</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1150,19 +1141,15 @@
         <v>27</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="29"/>
+        <v>84</v>
+      </c>
+      <c r="D37" s="30"/>
     </row>
     <row r="38" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12"/>
-      <c r="B38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="28"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="19"/>
     </row>
     <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12"/>
@@ -1235,10 +1222,10 @@
     <mergeCell ref="A3:A14"/>
     <mergeCell ref="D3:D14"/>
     <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D36:D38"/>
     <mergeCell ref="D34:D35"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D15:D28"/>
+    <mergeCell ref="D36:D37"/>
   </mergeCells>
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1296,7 +1283,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>13</v>
@@ -1308,7 +1295,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>15</v>
@@ -1317,13 +1304,13 @@
         <v>16</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>17</v>
@@ -1338,7 +1325,7 @@
         <v>19</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>20</v>
@@ -1359,10 +1346,10 @@
         <v>21</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>6</v>
